--- a/frontend/src/data.xlsx
+++ b/frontend/src/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\project-on-github\business_management\frontend\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DA396B-DC36-425D-865D-929DE3A5F86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5688CE-BE48-404A-BAD3-EA5FF56AFCD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CC5FB67B-5B86-46C8-BD29-0FEF49274CE8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="241">
   <si>
     <t>project</t>
   </si>
@@ -747,6 +747,18 @@
   </si>
   <si>
     <t>setting</t>
+  </si>
+  <si>
+    <t>md_policy_kpi</t>
+  </si>
+  <si>
+    <t>md_policy_id</t>
+  </si>
+  <si>
+    <t>policy_id</t>
+  </si>
+  <si>
+    <t>is_deleted</t>
   </si>
 </sst>
 </file>
@@ -882,7 +894,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -947,10 +959,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2497,7 +2506,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866AE55C-4BB2-4382-8851-661DDF4A5BC5}">
-  <dimension ref="B1:G152"/>
+  <dimension ref="B1:G161"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" style="2" bestFit="1" customWidth="1"/>
@@ -2710,8 +2719,10 @@
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="15"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="23" t="s">
+      <c r="C14" s="1">
+        <v>4</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -2723,56 +2734,58 @@
     <row r="15" spans="2:7">
       <c r="B15" s="15"/>
       <c r="C15" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="16" spans="2:7">
       <c r="B16" s="15"/>
       <c r="C16" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="17" spans="2:7">
       <c r="B17" s="15"/>
       <c r="C17" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="F17" s="1"/>
     </row>
     <row r="18" spans="2:7">
       <c r="B18" s="15"/>
       <c r="C18" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -2780,272 +2793,278 @@
     <row r="19" spans="2:7">
       <c r="B19" s="15"/>
       <c r="C19" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>22</v>
+        <v>240</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="2:7">
       <c r="B20" s="15"/>
       <c r="C20" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="15"/>
+      <c r="C21" s="1">
+        <v>11</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="15"/>
+      <c r="C22" s="1">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="15"/>
+      <c r="C23" s="1">
+        <v>13</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="3">
-        <v>1</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="17"/>
-      <c r="C22" s="4">
-        <v>2</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="17"/>
-      <c r="C23" s="4">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="17"/>
-      <c r="C24" s="3">
-        <v>4</v>
+      <c r="B24" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="1"/>
+      <c r="F24" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="17"/>
-      <c r="C25" s="4">
-        <v>5</v>
+      <c r="C25" s="1">
+        <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F25" s="1"/>
-      <c r="G25" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="G25" s="1"/>
     </row>
     <row r="26" spans="2:7">
       <c r="B26" s="17"/>
-      <c r="C26" s="4">
-        <v>6</v>
+      <c r="C26" s="1">
+        <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>33</v>
+        <v>239</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1"/>
-      <c r="G26" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="G26" s="1"/>
     </row>
     <row r="27" spans="2:7">
       <c r="B27" s="17"/>
-      <c r="C27" s="3">
-        <v>7</v>
+      <c r="C27" s="1">
+        <v>4</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="2:7">
       <c r="B28" s="17"/>
-      <c r="C28" s="4">
-        <v>8</v>
+      <c r="C28" s="1">
+        <v>5</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="18"/>
-      <c r="C29" s="4">
-        <v>9</v>
+      <c r="B29" s="17"/>
+      <c r="C29" s="1">
+        <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="3"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="1">
+        <v>7</v>
+      </c>
       <c r="D30" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
     <row r="31" spans="2:7">
       <c r="B31" s="17"/>
-      <c r="C31" s="4"/>
+      <c r="C31" s="1">
+        <v>8</v>
+      </c>
       <c r="D31" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="17"/>
-      <c r="C32" s="4"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>9</v>
+      </c>
       <c r="D32" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="18"/>
-      <c r="C33" s="5"/>
+      <c r="B33" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
       <c r="D33" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="3">
-        <v>1</v>
+      <c r="B34" s="17"/>
+      <c r="C34" s="1">
+        <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="17"/>
-      <c r="C35" s="4">
-        <v>2</v>
+      <c r="C35" s="1">
+        <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="17"/>
-      <c r="C36" s="4">
-        <v>3</v>
+      <c r="C36" s="1">
+        <v>4</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="18"/>
-      <c r="C37" s="5">
-        <v>4</v>
+      <c r="B37" s="17"/>
+      <c r="C37" s="1">
+        <v>5</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>17</v>
@@ -3054,290 +3073,278 @@
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="11" t="s">
-        <v>41</v>
-      </c>
+      <c r="B38" s="18"/>
       <c r="C38" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="1" t="s">
+      <c r="E39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="1"/>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="11"/>
-      <c r="C39" s="1">
-        <v>2</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="17"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-    </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="11"/>
-      <c r="C40" s="1">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="11"/>
-      <c r="C41" s="1">
-        <v>4</v>
-      </c>
+      <c r="B41" s="17"/>
+      <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="2:7">
-      <c r="B42" s="11"/>
-      <c r="C42" s="1">
-        <v>5</v>
-      </c>
+      <c r="B42" s="18"/>
+      <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
     <row r="43" spans="2:7">
-      <c r="B43" s="11"/>
-      <c r="C43" s="1">
-        <v>6</v>
+      <c r="B43" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G43" s="1"/>
     </row>
     <row r="44" spans="2:7">
-      <c r="B44" s="11"/>
-      <c r="C44" s="1">
-        <v>7</v>
+      <c r="B44" s="17"/>
+      <c r="C44" s="4">
+        <v>2</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
     <row r="45" spans="2:7">
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="17"/>
+      <c r="C45" s="4">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="18"/>
+      <c r="C46" s="5">
+        <v>4</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="2:7">
+      <c r="B48" s="11"/>
+      <c r="C48" s="1">
+        <v>2</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="2:7">
+      <c r="B49" s="11"/>
+      <c r="C49" s="1">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="11"/>
+      <c r="C50" s="1">
+        <v>4</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="2:7">
+      <c r="B51" s="11"/>
+      <c r="C51" s="1">
+        <v>5</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="2:7">
+      <c r="B52" s="11"/>
+      <c r="C52" s="1">
+        <v>6</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="2:7">
+      <c r="B53" s="11"/>
+      <c r="C53" s="1">
+        <v>7</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="2:7">
+      <c r="B54" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="1">
-        <v>1</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="C54" s="1">
+        <v>1</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="1" t="s">
+      <c r="E54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G45" s="1"/>
-    </row>
-    <row r="46" spans="2:7">
-      <c r="B46" s="9"/>
-      <c r="C46" s="1">
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="2:7">
+      <c r="B55" s="9"/>
+      <c r="C55" s="1">
         <v>2</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E55" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1" t="s">
+      <c r="F55" s="1"/>
+      <c r="G55" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
-      <c r="B47" s="9"/>
-      <c r="C47" s="1">
+    <row r="56" spans="2:7">
+      <c r="B56" s="9"/>
+      <c r="C56" s="1">
         <v>3</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-    </row>
-    <row r="48" spans="2:7">
-      <c r="B48" s="9"/>
-      <c r="C48" s="1">
-        <v>4</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G48" s="1"/>
-    </row>
-    <row r="49" spans="2:7">
-      <c r="B49" s="9"/>
-      <c r="C49" s="1">
-        <v>5</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="2:7">
-      <c r="B50" s="9"/>
-      <c r="C50" s="1">
-        <v>6</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-    </row>
-    <row r="51" spans="2:7">
-      <c r="B51" s="9"/>
-      <c r="C51" s="1">
-        <v>7</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G51" s="1"/>
-    </row>
-    <row r="52" spans="2:7">
-      <c r="B52" s="9"/>
-      <c r="C52" s="1">
-        <v>8</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-    </row>
-    <row r="53" spans="2:7">
-      <c r="B53" s="9"/>
-      <c r="C53" s="1">
-        <v>9</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G53" s="1"/>
-    </row>
-    <row r="54" spans="2:7">
-      <c r="B54" s="10"/>
-      <c r="C54" s="1">
-        <v>10</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-    </row>
-    <row r="55" spans="2:7">
-      <c r="B55" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C55" s="1">
-        <v>1</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G55" s="1"/>
-    </row>
-    <row r="56" spans="2:7">
-      <c r="B56" s="11"/>
-      <c r="C56" s="1">
-        <v>2</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>14</v>
@@ -3346,124 +3353,136 @@
       <c r="G56" s="1"/>
     </row>
     <row r="57" spans="2:7">
-      <c r="B57" s="11"/>
+      <c r="B57" s="9"/>
       <c r="C57" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F57" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="G57" s="1"/>
     </row>
     <row r="58" spans="2:7">
-      <c r="B58" s="11"/>
+      <c r="B58" s="9"/>
       <c r="C58" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F58" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="G58" s="1"/>
     </row>
     <row r="59" spans="2:7">
-      <c r="B59" s="11"/>
+      <c r="B59" s="9"/>
       <c r="C59" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F59" s="1"/>
-      <c r="G59" s="6"/>
+      <c r="G59" s="1"/>
     </row>
     <row r="60" spans="2:7">
-      <c r="B60" s="11"/>
+      <c r="B60" s="9"/>
       <c r="C60" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G60" s="1"/>
+    </row>
+    <row r="61" spans="2:7">
+      <c r="B61" s="9"/>
+      <c r="C61" s="1">
         <v>8</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-    </row>
-    <row r="61" spans="2:7">
-      <c r="B61" s="11"/>
-      <c r="C61" s="1">
-        <v>7</v>
-      </c>
       <c r="D61" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
     </row>
     <row r="62" spans="2:7">
-      <c r="B62" s="11"/>
+      <c r="B62" s="9"/>
       <c r="C62" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F62" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="G62" s="1"/>
     </row>
     <row r="63" spans="2:7">
-      <c r="B63" s="11"/>
+      <c r="B63" s="10"/>
       <c r="C63" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
     <row r="64" spans="2:7">
-      <c r="B64" s="11"/>
+      <c r="B64" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="C64" s="1">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E64" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F64" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G64" s="1"/>
     </row>
     <row r="65" spans="2:7">
       <c r="B65" s="11"/>
       <c r="C65" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>14</v>
@@ -3474,13 +3493,13 @@
     <row r="66" spans="2:7">
       <c r="B66" s="11"/>
       <c r="C66" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
@@ -3488,10 +3507,10 @@
     <row r="67" spans="2:7">
       <c r="B67" s="11"/>
       <c r="C67" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>14</v>
@@ -3502,27 +3521,27 @@
     <row r="68" spans="2:7">
       <c r="B68" s="11"/>
       <c r="C68" s="1">
+        <v>5</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
+      <c r="G68" s="6"/>
     </row>
     <row r="69" spans="2:7">
       <c r="B69" s="11"/>
       <c r="C69" s="1">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
@@ -3530,13 +3549,13 @@
     <row r="70" spans="2:7">
       <c r="B70" s="11"/>
       <c r="C70" s="1">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
@@ -3544,13 +3563,13 @@
     <row r="71" spans="2:7">
       <c r="B71" s="11"/>
       <c r="C71" s="1">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -3558,29 +3577,27 @@
     <row r="72" spans="2:7">
       <c r="B72" s="11"/>
       <c r="C72" s="1">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
     <row r="73" spans="2:7">
       <c r="B73" s="11"/>
       <c r="C73" s="1">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -3588,58 +3605,52 @@
     <row r="74" spans="2:7">
       <c r="B74" s="11"/>
       <c r="C74" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
     <row r="75" spans="2:7">
       <c r="B75" s="11"/>
       <c r="C75" s="1">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
     <row r="76" spans="2:7">
-      <c r="B76" s="11" t="s">
-        <v>68</v>
-      </c>
+      <c r="B76" s="11"/>
       <c r="C76" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
     <row r="77" spans="2:7">
       <c r="B77" s="11"/>
       <c r="C77" s="1">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>17</v>
@@ -3650,10 +3661,10 @@
     <row r="78" spans="2:7">
       <c r="B78" s="11"/>
       <c r="C78" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>17</v>
@@ -3664,10 +3675,10 @@
     <row r="79" spans="2:7">
       <c r="B79" s="11"/>
       <c r="C79" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>17</v>
@@ -3678,10 +3689,10 @@
     <row r="80" spans="2:7">
       <c r="B80" s="11"/>
       <c r="C80" s="1">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>17</v>
@@ -3692,27 +3703,29 @@
     <row r="81" spans="2:7">
       <c r="B81" s="11"/>
       <c r="C81" s="1">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F81" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="G81" s="1"/>
     </row>
     <row r="82" spans="2:7">
       <c r="B82" s="11"/>
       <c r="C82" s="1">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
@@ -3720,52 +3733,58 @@
     <row r="83" spans="2:7">
       <c r="B83" s="11"/>
       <c r="C83" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F83" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="G83" s="1"/>
     </row>
     <row r="84" spans="2:7">
       <c r="B84" s="11"/>
       <c r="C84" s="1">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
     </row>
     <row r="85" spans="2:7">
-      <c r="B85" s="11"/>
+      <c r="B85" s="11" t="s">
+        <v>68</v>
+      </c>
       <c r="C85" s="1">
+        <v>1</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F85" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G85" s="1"/>
     </row>
     <row r="86" spans="2:7">
       <c r="B86" s="11"/>
       <c r="C86" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>17</v>
@@ -3776,10 +3795,10 @@
     <row r="87" spans="2:7">
       <c r="B87" s="11"/>
       <c r="C87" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>17</v>
@@ -3790,10 +3809,10 @@
     <row r="88" spans="2:7">
       <c r="B88" s="11"/>
       <c r="C88" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>17</v>
@@ -3804,10 +3823,10 @@
     <row r="89" spans="2:7">
       <c r="B89" s="11"/>
       <c r="C89" s="1">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>17</v>
@@ -3818,10 +3837,10 @@
     <row r="90" spans="2:7">
       <c r="B90" s="11"/>
       <c r="C90" s="1">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>17</v>
@@ -3832,10 +3851,10 @@
     <row r="91" spans="2:7">
       <c r="B91" s="11"/>
       <c r="C91" s="1">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>17</v>
@@ -3846,10 +3865,10 @@
     <row r="92" spans="2:7">
       <c r="B92" s="11"/>
       <c r="C92" s="1">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>17</v>
@@ -3860,10 +3879,10 @@
     <row r="93" spans="2:7">
       <c r="B93" s="11"/>
       <c r="C93" s="1">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>17</v>
@@ -3874,10 +3893,10 @@
     <row r="94" spans="2:7">
       <c r="B94" s="11"/>
       <c r="C94" s="1">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>17</v>
@@ -3888,10 +3907,10 @@
     <row r="95" spans="2:7">
       <c r="B95" s="11"/>
       <c r="C95" s="1">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>17</v>
@@ -3902,10 +3921,10 @@
     <row r="96" spans="2:7">
       <c r="B96" s="11"/>
       <c r="C96" s="1">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>17</v>
@@ -3916,10 +3935,10 @@
     <row r="97" spans="2:7">
       <c r="B97" s="11"/>
       <c r="C97" s="1">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>17</v>
@@ -3930,10 +3949,10 @@
     <row r="98" spans="2:7">
       <c r="B98" s="11"/>
       <c r="C98" s="1">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>17</v>
@@ -3944,10 +3963,10 @@
     <row r="99" spans="2:7">
       <c r="B99" s="11"/>
       <c r="C99" s="1">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>17</v>
@@ -3958,10 +3977,10 @@
     <row r="100" spans="2:7">
       <c r="B100" s="11"/>
       <c r="C100" s="1">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>17</v>
@@ -3972,10 +3991,10 @@
     <row r="101" spans="2:7">
       <c r="B101" s="11"/>
       <c r="C101" s="1">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>17</v>
@@ -3986,10 +4005,10 @@
     <row r="102" spans="2:7">
       <c r="B102" s="11"/>
       <c r="C102" s="1">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>17</v>
@@ -4000,10 +4019,10 @@
     <row r="103" spans="2:7">
       <c r="B103" s="11"/>
       <c r="C103" s="1">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>17</v>
@@ -4014,10 +4033,10 @@
     <row r="104" spans="2:7">
       <c r="B104" s="11"/>
       <c r="C104" s="1">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>17</v>
@@ -4028,10 +4047,10 @@
     <row r="105" spans="2:7">
       <c r="B105" s="11"/>
       <c r="C105" s="1">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>17</v>
@@ -4042,10 +4061,10 @@
     <row r="106" spans="2:7">
       <c r="B106" s="11"/>
       <c r="C106" s="1">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>17</v>
@@ -4056,10 +4075,10 @@
     <row r="107" spans="2:7">
       <c r="B107" s="11"/>
       <c r="C107" s="1">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>17</v>
@@ -4070,10 +4089,10 @@
     <row r="108" spans="2:7">
       <c r="B108" s="11"/>
       <c r="C108" s="1">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>17</v>
@@ -4084,10 +4103,10 @@
     <row r="109" spans="2:7">
       <c r="B109" s="11"/>
       <c r="C109" s="1">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>17</v>
@@ -4098,218 +4117,232 @@
     <row r="110" spans="2:7">
       <c r="B110" s="11"/>
       <c r="C110" s="1">
+        <v>26</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+    </row>
+    <row r="111" spans="2:7">
+      <c r="B111" s="11"/>
+      <c r="C111" s="1">
+        <v>27</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+    </row>
+    <row r="112" spans="2:7">
+      <c r="B112" s="11"/>
+      <c r="C112" s="1">
+        <v>28</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+    </row>
+    <row r="113" spans="2:7">
+      <c r="B113" s="11"/>
+      <c r="C113" s="1">
+        <v>29</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+    </row>
+    <row r="114" spans="2:7">
+      <c r="B114" s="11"/>
+      <c r="C114" s="1">
+        <v>30</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+    </row>
+    <row r="115" spans="2:7">
+      <c r="B115" s="11"/>
+      <c r="C115" s="1">
+        <v>31</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+    </row>
+    <row r="116" spans="2:7">
+      <c r="B116" s="11"/>
+      <c r="C116" s="1">
+        <v>32</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+    </row>
+    <row r="117" spans="2:7">
+      <c r="B117" s="11"/>
+      <c r="C117" s="1">
+        <v>33</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+    </row>
+    <row r="118" spans="2:7">
+      <c r="B118" s="11"/>
+      <c r="C118" s="1">
+        <v>34</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+    </row>
+    <row r="119" spans="2:7">
+      <c r="B119" s="11"/>
+      <c r="C119" s="1">
         <v>35</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F110" s="1" t="s">
+      <c r="E119" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G110" s="1"/>
-    </row>
-    <row r="112" spans="2:7">
-      <c r="B112" s="12" t="s">
+      <c r="G119" s="1"/>
+    </row>
+    <row r="121" spans="2:7">
+      <c r="B121" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C112" s="1">
-        <v>1</v>
-      </c>
-      <c r="D112" s="1" t="s">
+      <c r="C121" s="1">
+        <v>1</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F112" s="1" t="s">
+      <c r="E121" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G112" s="1"/>
-    </row>
-    <row r="113" spans="2:7">
-      <c r="B113" s="13"/>
-      <c r="C113" s="1">
+      <c r="G121" s="1"/>
+    </row>
+    <row r="122" spans="2:7">
+      <c r="B122" s="13"/>
+      <c r="C122" s="1">
         <v>2</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D122" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E122" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F113" s="1" t="s">
+      <c r="F122" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G113" s="1"/>
-    </row>
-    <row r="114" spans="2:7">
-      <c r="B114" s="13"/>
-      <c r="C114" s="1">
+      <c r="G122" s="1"/>
+    </row>
+    <row r="123" spans="2:7">
+      <c r="B123" s="13"/>
+      <c r="C123" s="1">
         <v>3</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E123" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F114" s="1" t="s">
+      <c r="F123" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G114" s="1"/>
-    </row>
-    <row r="115" spans="2:7">
-      <c r="B115" s="14"/>
-      <c r="C115" s="1">
+      <c r="G123" s="1"/>
+    </row>
+    <row r="124" spans="2:7">
+      <c r="B124" s="14"/>
+      <c r="C124" s="1">
         <v>4</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="D124" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F115" s="1" t="s">
+      <c r="E124" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G115" s="1"/>
-    </row>
-    <row r="119" spans="2:7">
-      <c r="B119" s="1" t="s">
+      <c r="G124" s="1"/>
+    </row>
+    <row r="128" spans="2:7">
+      <c r="B128" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G119" s="1"/>
-    </row>
-    <row r="120" spans="2:7">
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F120" s="1"/>
-      <c r="G120" s="1"/>
-    </row>
-    <row r="121" spans="2:7">
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F121" s="1"/>
-      <c r="G121" s="1"/>
-    </row>
-    <row r="122" spans="2:7">
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-    </row>
-    <row r="123" spans="2:7">
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="124" spans="2:7">
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F124" s="1"/>
-      <c r="G124" s="1"/>
-    </row>
-    <row r="125" spans="2:7">
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-    </row>
-    <row r="126" spans="2:7">
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-    </row>
-    <row r="127" spans="2:7">
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F127" s="1"/>
-      <c r="G127" s="1"/>
-    </row>
-    <row r="128" spans="2:7">
-      <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="D128" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F128" s="1"/>
-      <c r="G128" s="1" t="s">
-        <v>119</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G128" s="1"/>
     </row>
     <row r="129" spans="2:7">
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
       <c r="D129" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>14</v>
@@ -4318,12 +4351,10 @@
       <c r="G129" s="1"/>
     </row>
     <row r="130" spans="2:7">
-      <c r="B130" s="1" t="s">
-        <v>121</v>
-      </c>
+      <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="D130" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>11</v>
@@ -4335,7 +4366,7 @@
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
       <c r="D131" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>11</v>
@@ -4347,22 +4378,24 @@
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F132" s="1"/>
-      <c r="G132" s="1"/>
+      <c r="G132" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="133" spans="2:7">
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
       <c r="D133" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
@@ -4371,24 +4404,22 @@
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
       <c r="D134" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
     </row>
     <row r="135" spans="2:7">
-      <c r="B135" s="1" t="s">
-        <v>125</v>
-      </c>
+      <c r="B135" s="1"/>
       <c r="C135" s="1"/>
       <c r="D135" s="1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
@@ -4397,61 +4428,59 @@
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
     </row>
     <row r="137" spans="2:7">
       <c r="B137" s="1"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4" t="s">
-        <v>128</v>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F137" s="1"/>
-      <c r="G137" s="1"/>
+      <c r="G137" s="1" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="138" spans="2:7">
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F138" s="1"/>
-      <c r="G138" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="G138" s="1"/>
     </row>
     <row r="139" spans="2:7">
-      <c r="B139" s="1"/>
+      <c r="B139" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="C139" s="1"/>
       <c r="D139" s="1" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F139" s="1"/>
-      <c r="G139" s="1" t="s">
-        <v>132</v>
-      </c>
+      <c r="G139" s="1"/>
     </row>
     <row r="140" spans="2:7">
-      <c r="B140" s="1" t="s">
-        <v>133</v>
-      </c>
+      <c r="B140" s="1"/>
       <c r="C140" s="1"/>
       <c r="D140" s="1" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>11</v>
@@ -4463,7 +4492,7 @@
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
       <c r="D141" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>11</v>
@@ -4475,10 +4504,10 @@
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
       <c r="D142" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
@@ -4487,48 +4516,48 @@
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
       <c r="D143" s="1" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
     </row>
     <row r="144" spans="2:7">
-      <c r="B144" s="1"/>
+      <c r="B144" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
     </row>
     <row r="145" spans="2:7">
-      <c r="B145" s="1" t="s">
-        <v>135</v>
-      </c>
+      <c r="B145" s="1"/>
       <c r="C145" s="1"/>
       <c r="D145" s="1" t="s">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
     </row>
     <row r="146" spans="2:7">
       <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
-      <c r="D146" s="1" t="s">
-        <v>122</v>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
@@ -4537,34 +4566,40 @@
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
       <c r="D147" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F147" s="1"/>
-      <c r="G147" s="1"/>
+      <c r="G147" s="1" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="148" spans="2:7">
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
       <c r="D148" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F148" s="1"/>
-      <c r="G148" s="1"/>
+      <c r="G148" s="1" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="149" spans="2:7">
-      <c r="B149" s="1"/>
+      <c r="B149" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="C149" s="1"/>
       <c r="D149" s="1" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
@@ -4573,54 +4608,165 @@
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
       <c r="D150" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="F150" s="1"/>
       <c r="G150" s="1"/>
     </row>
     <row r="151" spans="2:7">
-      <c r="B151" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="B151" s="1"/>
       <c r="C151" s="1"/>
       <c r="D151" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F151" s="1"/>
-      <c r="G151" s="1" t="s">
-        <v>140</v>
-      </c>
+      <c r="G151" s="1"/>
     </row>
     <row r="152" spans="2:7">
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
       <c r="D152" s="1" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
     </row>
+    <row r="153" spans="2:7">
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153" s="1"/>
+      <c r="G153" s="1"/>
+    </row>
+    <row r="154" spans="2:7">
+      <c r="B154" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" s="1"/>
+      <c r="G154" s="1"/>
+    </row>
+    <row r="155" spans="2:7">
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155" s="1"/>
+      <c r="G155" s="1"/>
+    </row>
+    <row r="156" spans="2:7">
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F156" s="1"/>
+      <c r="G156" s="1"/>
+    </row>
+    <row r="157" spans="2:7">
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F157" s="1"/>
+      <c r="G157" s="1"/>
+    </row>
+    <row r="158" spans="2:7">
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F158" s="1"/>
+      <c r="G158" s="1"/>
+    </row>
+    <row r="159" spans="2:7">
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F159" s="1"/>
+      <c r="G159" s="1"/>
+    </row>
+    <row r="160" spans="2:7">
+      <c r="B160" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="161" spans="2:7">
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B45:B54"/>
-    <mergeCell ref="B55:B75"/>
-    <mergeCell ref="B76:B110"/>
-    <mergeCell ref="B112:B115"/>
+  <mergeCells count="11">
+    <mergeCell ref="B54:B63"/>
+    <mergeCell ref="B64:B84"/>
+    <mergeCell ref="B85:B119"/>
+    <mergeCell ref="B121:B124"/>
     <mergeCell ref="B2:B10"/>
-    <mergeCell ref="B11:B20"/>
-    <mergeCell ref="B21:B29"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="B11:B23"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="B47:B53"/>
+    <mergeCell ref="B33:B38"/>
+    <mergeCell ref="B24:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/frontend/src/data.xlsx
+++ b/frontend/src/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\project-on-github\business_management\frontend\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5688CE-BE48-404A-BAD3-EA5FF56AFCD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D66BD4-24D5-485F-9DFD-0D781AB05A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CC5FB67B-5B86-46C8-BD29-0FEF49274CE8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="250">
   <si>
     <t>project</t>
   </si>
@@ -759,6 +759,33 @@
   </si>
   <si>
     <t>is_deleted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">project </t>
+  </si>
+  <si>
+    <t>Strategic Alignment</t>
+  </si>
+  <si>
+    <t>Problem / Opportunity</t>
+  </si>
+  <si>
+    <t>Objective</t>
+  </si>
+  <si>
+    <t>what</t>
+  </si>
+  <si>
+    <t>Solution</t>
+  </si>
+  <si>
+    <t>how</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Scope</t>
   </si>
 </sst>
 </file>
@@ -894,7 +921,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -957,9 +984,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2506,7 +2530,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866AE55C-4BB2-4382-8851-661DDF4A5BC5}">
-  <dimension ref="B1:G161"/>
+  <dimension ref="B1:G169"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" style="2" bestFit="1" customWidth="1"/>
@@ -2722,7 +2746,7 @@
       <c r="C14" s="1">
         <v>4</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -4753,6 +4777,45 @@
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
+    </row>
+    <row r="164" spans="2:7">
+      <c r="B164" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="165" spans="2:7">
+      <c r="D165" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="166" spans="2:7">
+      <c r="D166" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="167" spans="2:7">
+      <c r="D167" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="168" spans="2:7">
+      <c r="D168" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="169" spans="2:7">
+      <c r="D169" s="2" t="s">
+        <v>249</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
